--- a/artfynd/A 41652-2023 artfynd.xlsx
+++ b/artfynd/A 41652-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41652-2023 artfynd.xlsx
+++ b/artfynd/A 41652-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>61679917</v>
       </c>
       <c r="B2" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751362.4184343785</v>
+        <v>751362</v>
       </c>
       <c r="R2" t="n">
-        <v>7427706.501544613</v>
+        <v>7427707</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -758,19 +753,9 @@
           <t>2016-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -803,37 +788,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115527655</v>
+        <v>115527646</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>863</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia austerodes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Räsänen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751527</v>
+        <v>751217</v>
       </c>
       <c r="R3" t="n">
-        <v>7427548</v>
+        <v>7427553</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115522656</v>
+        <v>115522638</v>
       </c>
       <c r="B4" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751402</v>
+        <v>751242</v>
       </c>
       <c r="R4" t="n">
-        <v>7427311</v>
+        <v>7427530</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1021,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115522638</v>
+        <v>115527648</v>
       </c>
       <c r="B5" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,19 +1025,22 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>...Rudnevárre, Lu lm</t>
+          <t>Rudnevárre, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>751242</v>
+        <v>751342</v>
       </c>
       <c r="R5" t="n">
-        <v>7427530</v>
+        <v>7427622</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,44 +1067,50 @@
           <t>2024-03-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-03-29</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Ida Jansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Ida Jansson, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115522634</v>
+        <v>115527650</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,37 +1118,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>...Rudnevárre, Lu lm</t>
+          <t>Rudnevárre, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>751292</v>
+        <v>751280</v>
       </c>
       <c r="R6" t="n">
-        <v>7427455</v>
+        <v>7427639</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,14 +1178,19 @@
           <t>2024-03-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-03-29</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Tydliga ringhack på tall</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,37 +1199,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Ida Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Ida Jansson, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115522662</v>
+        <v>115522640</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1270,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>751529</v>
+        <v>751659</v>
       </c>
       <c r="R7" t="n">
-        <v>7427577</v>
+        <v>7427474</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1300,12 +1283,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,6 +1297,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1332,56 +1316,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115527648</v>
+        <v>115522652</v>
       </c>
       <c r="B8" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rudnevárre, Lu lm</t>
+          <t>...Rudnevárre, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>751342</v>
+        <v>751489</v>
       </c>
       <c r="R8" t="n">
-        <v>7427622</v>
+        <v>7427225</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,77 +1384,61 @@
           <t>2024-03-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-03-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ida Jansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ida Jansson, Cecilia Lundin</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115522633</v>
+        <v>115522654</v>
       </c>
       <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1488,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>751233</v>
+        <v>751451</v>
       </c>
       <c r="R9" t="n">
-        <v>7427378</v>
+        <v>7427229</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1524,11 +1484,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Tydliga ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,15 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115527646</v>
+        <v>115522656</v>
       </c>
       <c r="B10" t="n">
-        <v>78588</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,40 +1521,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>863</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia austerodes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Räsänen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rudnevárre, Lu lm</t>
+          <t>...Rudnevárre, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>751217</v>
+        <v>751402</v>
       </c>
       <c r="R10" t="n">
-        <v>7427553</v>
+        <v>7427311</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,59 +1578,43 @@
           <t>2024-03-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-03-29</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ida Jansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ida Jansson, Cecilia Lundin</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115527653</v>
+        <v>115522657</v>
       </c>
       <c r="B11" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1705,22 +1636,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rudnevárre, Lu lm</t>
+          <t>...Rudnevárre, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751437</v>
+        <v>751283</v>
       </c>
       <c r="R11" t="n">
-        <v>7427639</v>
+        <v>7427658</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,59 +1675,43 @@
           <t>2024-03-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-03-29</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ida Jansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ida Jansson, Cecilia Lundin</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115522660</v>
+        <v>115522658</v>
       </c>
       <c r="B12" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1827,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751190</v>
+        <v>751305</v>
       </c>
       <c r="R12" t="n">
-        <v>7427540</v>
+        <v>7427660</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1889,19 +1801,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115522664</v>
+        <v>115522659</v>
       </c>
       <c r="B13" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1929,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751557</v>
+        <v>751170</v>
       </c>
       <c r="R13" t="n">
-        <v>7427569</v>
+        <v>7427554</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1991,19 +1898,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115522658</v>
+        <v>115522660</v>
       </c>
       <c r="B14" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2031,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751305</v>
+        <v>751190</v>
       </c>
       <c r="R14" t="n">
-        <v>7427660</v>
+        <v>7427540</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2093,19 +1995,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115522666</v>
+        <v>115522661</v>
       </c>
       <c r="B15" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2133,10 +2030,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>751630</v>
+        <v>751489</v>
       </c>
       <c r="R15" t="n">
-        <v>7427458</v>
+        <v>7427615</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2163,12 +2060,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,56 +2092,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115527647</v>
+        <v>115522662</v>
       </c>
       <c r="B16" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rudnevárre, Lu lm</t>
+          <t>...Rudnevárre, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751319</v>
+        <v>751529</v>
       </c>
       <c r="R16" t="n">
-        <v>7427664</v>
+        <v>7427577</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2271,94 +2160,74 @@
           <t>2024-03-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-03-29</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ida Jansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ida Jansson, Cecilia Lundin</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115522630</v>
+        <v>115522664</v>
       </c>
       <c r="B17" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>...Rudnevárre, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751227</v>
+        <v>751557</v>
       </c>
       <c r="R17" t="n">
-        <v>7427426</v>
+        <v>7427569</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2391,11 +2260,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tydliga ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,19 +2286,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115522652</v>
+        <v>115522665</v>
       </c>
       <c r="B18" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2462,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751489</v>
+        <v>751564</v>
       </c>
       <c r="R18" t="n">
-        <v>7427225</v>
+        <v>7427560</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2524,19 +2383,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115522640</v>
+        <v>115522666</v>
       </c>
       <c r="B19" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2564,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>751659</v>
+        <v>751630</v>
       </c>
       <c r="R19" t="n">
-        <v>7427474</v>
+        <v>7427458</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2608,7 +2462,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2627,19 +2480,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115527656</v>
+        <v>115527653</v>
       </c>
       <c r="B20" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2670,10 +2518,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751554</v>
+        <v>751437</v>
       </c>
       <c r="R20" t="n">
-        <v>7427537</v>
+        <v>7427639</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2553,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,7 +2563,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2743,19 +2591,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115522659</v>
+        <v>115527655</v>
       </c>
       <c r="B21" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2777,19 +2620,22 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>...Rudnevárre, Lu lm</t>
+          <t>Rudnevárre, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751170</v>
+        <v>751527</v>
       </c>
       <c r="R21" t="n">
-        <v>7427554</v>
+        <v>7427548</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2816,48 +2662,54 @@
           <t>2024-03-29</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-03-29</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Ida Jansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Ida Jansson, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115522661</v>
+        <v>115527656</v>
       </c>
       <c r="B22" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2879,19 +2731,22 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>...Rudnevárre, Lu lm</t>
+          <t>Rudnevárre, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751489</v>
+        <v>751554</v>
       </c>
       <c r="R22" t="n">
-        <v>7427615</v>
+        <v>7427537</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2918,44 +2773,50 @@
           <t>2024-03-29</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-03-29</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Ida Jansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Ida Jansson, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115522654</v>
+        <v>115527647</v>
       </c>
       <c r="B23" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,37 +2824,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>...Rudnevárre, Lu lm</t>
+          <t>Rudnevárre, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751451</v>
+        <v>751319</v>
       </c>
       <c r="R23" t="n">
-        <v>7427229</v>
+        <v>7427664</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3020,44 +2884,50 @@
           <t>2024-03-29</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-03-29</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Ida Jansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Ida Jansson, Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115522665</v>
+        <v>115522630</v>
       </c>
       <c r="B24" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3065,34 +2935,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>...Rudnevárre, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751564</v>
+        <v>751227</v>
       </c>
       <c r="R24" t="n">
-        <v>7427560</v>
+        <v>7427426</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3127,6 +3001,11 @@
           <t>2024-03-29</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Tydliga ringhack</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3148,6 +3027,210 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>115522633</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>...Rudnevárre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>751233</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7427378</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Tydliga ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>115522634</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>...Rudnevárre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>751292</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7427455</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Tydliga ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41652-2023 artfynd.xlsx
+++ b/artfynd/A 41652-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61679917</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115527646</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522638</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115527648</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115527650</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522640</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522652</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,6 +1547,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522654</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,6 +1649,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522656</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522657</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522658</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1895,6 +1955,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522659</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1992,6 +2057,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522660</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2089,6 +2159,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522661</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2186,6 +2261,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522662</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2283,6 +2363,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522664</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2380,6 +2465,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522665</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2477,6 +2567,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522666</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2588,6 +2683,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115527653</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2699,6 +2799,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115527655</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2810,6 +2915,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115527656</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2921,6 +3031,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115527647</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3027,6 +3142,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522630</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3129,6 +3249,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522633</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3231,8 +3356,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115522634</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>